--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.68418022773272</v>
+        <v>9.211179287006567</v>
       </c>
       <c r="D2" t="n">
-        <v>55.73562736290209</v>
+        <v>9.05703944647159</v>
       </c>
       <c r="E2" t="n">
-        <v>14.14206956674954</v>
+        <v>2.298086304596801</v>
       </c>
       <c r="F2" t="n">
-        <v>13.96027644600376</v>
+        <v>2.268544922475611</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>6.702368773915725</v>
+        <v>1.089134925761305</v>
       </c>
       <c r="D3" t="n">
-        <v>6.936462121072417</v>
+        <v>1.127175094674268</v>
       </c>
       <c r="E3" t="n">
-        <v>14.14206956674954</v>
+        <v>2.298086304596801</v>
       </c>
       <c r="F3" t="n">
-        <v>13.96027644600376</v>
+        <v>2.268544922475611</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.79223825916264</v>
+        <v>6.62873871711393</v>
       </c>
       <c r="D4" t="n">
-        <v>41.18409558436829</v>
+        <v>6.692415532459846</v>
       </c>
       <c r="E4" t="n">
-        <v>14.14206956674954</v>
+        <v>2.298086304596801</v>
       </c>
       <c r="F4" t="n">
-        <v>13.96027644600376</v>
+        <v>2.268544922475611</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.87035232572734</v>
+        <v>4.366432252930693</v>
       </c>
       <c r="D5" t="n">
-        <v>26.83730888519356</v>
+        <v>4.361062693843954</v>
       </c>
       <c r="E5" t="n">
-        <v>14.14206956674954</v>
+        <v>2.298086304596801</v>
       </c>
       <c r="F5" t="n">
-        <v>13.96027644600376</v>
+        <v>2.268544922475611</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.60594890731995</v>
+        <v>4.485966697439492</v>
       </c>
       <c r="D6" t="n">
-        <v>27.45348901309159</v>
+        <v>4.461191964627384</v>
       </c>
       <c r="E6" t="n">
-        <v>14.14206956674954</v>
+        <v>2.298086304596801</v>
       </c>
       <c r="F6" t="n">
-        <v>13.96027644600376</v>
+        <v>2.268544922475611</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>13.74564385145733</v>
+        <v>2.233667125861815</v>
       </c>
       <c r="D7" t="n">
-        <v>13.58508904100471</v>
+        <v>2.207576969163265</v>
       </c>
       <c r="E7" t="n">
-        <v>14.14206956674954</v>
+        <v>2.298086304596801</v>
       </c>
       <c r="F7" t="n">
-        <v>13.96027644600376</v>
+        <v>2.268544922475611</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.54363824863135</v>
+        <v>6.100841215402595</v>
       </c>
       <c r="D8" t="n">
-        <v>37.41511724796433</v>
+        <v>6.079956552794204</v>
       </c>
       <c r="E8" t="n">
-        <v>14.14206956674954</v>
+        <v>2.298086304596801</v>
       </c>
       <c r="F8" t="n">
-        <v>13.96027644600376</v>
+        <v>2.268544922475611</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.2013914258524</v>
+        <v>5.557726106701015</v>
       </c>
       <c r="D9" t="n">
-        <v>34.13383201128175</v>
+        <v>5.546747701833284</v>
       </c>
       <c r="E9" t="n">
-        <v>14.14206956674954</v>
+        <v>2.298086304596801</v>
       </c>
       <c r="F9" t="n">
-        <v>13.96027644600376</v>
+        <v>2.268544922475611</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>39.79797626919271</v>
+        <v>6.467171143743816</v>
       </c>
       <c r="D10" t="n">
-        <v>39.77804788487796</v>
+        <v>6.463932781292669</v>
       </c>
       <c r="E10" t="n">
-        <v>14.14206956674954</v>
+        <v>2.298086304596801</v>
       </c>
       <c r="F10" t="n">
-        <v>13.96027644600376</v>
+        <v>2.268544922475611</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
